--- a/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,34</t>
+          <t>-0,0; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,65</t>
+          <t>-0,45; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,0</t>
+          <t>-0,07; 4,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,69</t>
+          <t>-1,16; 3,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,9</t>
+          <t>1,61; 7,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,98</t>
+          <t>-1,45; 2,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,42</t>
+          <t>-0,05; 3,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,65</t>
+          <t>1,06; 4,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,6</t>
+          <t>-0,26; 2,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 501,86</t>
+          <t>-13,6; 443,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 341,2</t>
+          <t>-26,88; 400,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 464,49</t>
+          <t>-13,2; 464,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 665,47</t>
+          <t>-58,53; 474,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,95; 1330,85</t>
+          <t>39,18; 976,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 324,22</t>
+          <t>-54,77; 344,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 330,41</t>
+          <t>-4,46; 293,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,55; 444,75</t>
+          <t>42,57; 443,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 246,21</t>
+          <t>-13,04; 244,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,36</t>
+          <t>-2,08; 3,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,81</t>
+          <t>-2,68; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,45</t>
+          <t>-3,49; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,63</t>
+          <t>-1,61; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,8</t>
+          <t>-1,82; 3,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,78</t>
+          <t>-1,34; 3,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,96</t>
+          <t>-0,96; 3,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,63</t>
+          <t>-1,38; 2,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,77</t>
+          <t>-1,83; 1,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 161,37</t>
+          <t>-45,74; 166,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 161,23</t>
+          <t>-55,68; 147,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,44; 80,25</t>
+          <t>-72,11; 87,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 218,34</t>
+          <t>-40,33; 189,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 182,16</t>
+          <t>-41,9; 168,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 182,92</t>
+          <t>-31,62; 174,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 113,61</t>
+          <t>-24,26; 124,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 116,9</t>
+          <t>-33,26; 104,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 71,59</t>
+          <t>-40,62; 69,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,23</t>
+          <t>-1,53; 2,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,4</t>
+          <t>0,37; 5,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,56</t>
+          <t>-3,26; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,48</t>
+          <t>-6,27; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 15,56</t>
+          <t>2,25; 16,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 3,13</t>
+          <t>-6,09; 3,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,82</t>
+          <t>-1,97; 1,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,64</t>
+          <t>1,86; 7,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,07</t>
+          <t>-3,11; 1,34</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,71; 116,35</t>
+          <t>-38,96; 135,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 261,68</t>
+          <t>6,77; 249,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,64; 61,94</t>
+          <t>-77,67; 73,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 101,08</t>
+          <t>-73,31; 121,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 512,93</t>
+          <t>15,14; 638,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,73; 142,64</t>
+          <t>-66,94; 126,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 79,16</t>
+          <t>-44,42; 69,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,09; 254,27</t>
+          <t>34,17; 252,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 31,79</t>
+          <t>-70,49; 46,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,5</t>
+          <t>-2,14; 0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,14</t>
+          <t>-0,01; 3,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,45</t>
+          <t>-1,41; 1,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,56</t>
+          <t>-1,74; 2,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,34</t>
+          <t>2,07; 7,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 56,28</t>
+          <t>-1,13; 49,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,94</t>
+          <t>-1,54; 0,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,33</t>
+          <t>1,52; 4,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 34,85</t>
+          <t>-0,38; 38,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,06; 22,5</t>
+          <t>-56,84; 26,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 128,39</t>
+          <t>-1,12; 134,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 64,59</t>
+          <t>-36,52; 52,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 79,32</t>
+          <t>-33,86; 73,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,17; 219,42</t>
+          <t>35,5; 229,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 1664,22</t>
+          <t>-22,56; 1613,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 33,36</t>
+          <t>-36,49; 27,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,7; 146,81</t>
+          <t>35,07; 147,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 1087,66</t>
+          <t>-10,45; 1165,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,83</t>
+          <t>-2,43; 2,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,57</t>
+          <t>-0,58; 4,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,3</t>
+          <t>-1,32; 4,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,56</t>
+          <t>-1,48; 3,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,66</t>
+          <t>7,71; 14,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,3</t>
+          <t>-2,45; 2,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,6</t>
+          <t>-1,22; 2,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,19</t>
+          <t>4,51; 9,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,29</t>
+          <t>-1,14; 2,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 156,92</t>
+          <t>-53,22; 145,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 246,86</t>
+          <t>-16,31; 272,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 237,77</t>
+          <t>-30,81; 250,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 98,74</t>
+          <t>-23,61; 96,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>112,85; 390,51</t>
+          <t>112,35; 365,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 58,72</t>
+          <t>-36,96; 60,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 73,16</t>
+          <t>-22,11; 73,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>80,56; 263,64</t>
+          <t>82,41; 266,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 63,37</t>
+          <t>-20,44; 74,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,37</t>
+          <t>-1,64; 2,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,66</t>
+          <t>-0,54; 4,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,76</t>
+          <t>-1,91; 3,56</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,41</t>
+          <t>-2,35; 1,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,41</t>
+          <t>4,55; 9,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,96</t>
+          <t>-2,0; 1,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,43</t>
+          <t>-1,67; 1,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,78</t>
+          <t>3,69; 7,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,61</t>
+          <t>-1,76; 1,56</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-71,98; 459,38</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-39,2; 679,35</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-33,59; 694,93</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 31,98</t>
+          <t>-37,73; 30,08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>74,59; 210,4</t>
+          <t>73,03; 214,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 43,2</t>
+          <t>-32,99; 42,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 37,24</t>
+          <t>-32,91; 33,23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>70,03; 199,65</t>
+          <t>67,69; 197,61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 40,93</t>
+          <t>-32,85; 41,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,12</t>
+          <t>-0,67; 1,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,76</t>
+          <t>0,81; 2,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,23</t>
+          <t>-0,63; 1,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,33</t>
+          <t>-0,8; 1,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,74</t>
+          <t>5,09; 7,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 22,33</t>
+          <t>-0,39; 22,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,97</t>
+          <t>-0,35; 1,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,97</t>
+          <t>3,37; 4,92</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 12,61</t>
+          <t>-0,13; 12,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 47,52</t>
+          <t>-20,8; 42,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>25,52; 117,87</t>
+          <t>24,88; 113,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 51,17</t>
+          <t>-19,9; 52,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 32,1</t>
+          <t>-15,8; 33,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>99,81; 189,93</t>
+          <t>96,73; 186,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 504,6</t>
+          <t>-8,77; 487,17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 29,08</t>
+          <t>-9,09; 31,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>80,36; 145,65</t>
+          <t>83,85; 149,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 361,99</t>
+          <t>-3,68; 367,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,32</t>
+          <t>0,09; 4,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,54</t>
+          <t>-0,54; 3,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,04</t>
+          <t>0,14; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,54</t>
+          <t>-1,22; 3,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,71</t>
+          <t>1,81; 7,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,09</t>
+          <t>-1,4; 2,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,17</t>
+          <t>0,1; 3,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,76</t>
+          <t>1,21; 4,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,54</t>
+          <t>-0,12; 2,59</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109,44%</t>
+          <t>112,86%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 443,43</t>
+          <t>-6,1; 424,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 400,48</t>
+          <t>-28,28; 410,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 464,21</t>
+          <t>-0,11; 413,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 474,13</t>
+          <t>-57,98; 587,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,18; 976,74</t>
+          <t>54,54; 1207,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,77; 344,11</t>
+          <t>-52,78; 300,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 293,54</t>
+          <t>1,11; 307,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,57; 443,07</t>
+          <t>48,35; 420,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 244,61</t>
+          <t>-5,27; 243,8</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>0,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,52</t>
+          <t>-2,26; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,09</t>
+          <t>-2,81; 2,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,59</t>
+          <t>-3,56; 1,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 4,24</t>
+          <t>-1,62; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,85</t>
+          <t>-2,02; 3,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,82</t>
+          <t>-1,48; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,15</t>
+          <t>-1,13; 3,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,6</t>
+          <t>-1,39; 2,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,68</t>
+          <t>-1,86; 1,75</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-27,76%</t>
+          <t>-27,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,01%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 166,17</t>
+          <t>-49,32; 171,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 147,16</t>
+          <t>-55,5; 144,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,11; 87,81</t>
+          <t>-72,82; 89,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 189,83</t>
+          <t>-39,77; 204,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 168,2</t>
+          <t>-44,04; 173,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 174,74</t>
+          <t>-34,16; 176,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 124,37</t>
+          <t>-26,39; 119,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 104,48</t>
+          <t>-34,46; 103,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 69,5</t>
+          <t>-41,16; 66,16</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,64</t>
+          <t>-1,86; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,18</t>
+          <t>0,41; 5,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,67</t>
+          <t>-1,1; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,82</t>
+          <t>-6,4; 2,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 16,08</t>
+          <t>2,24; 16,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,06</t>
+          <t>-5,65; 4,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,7</t>
+          <t>-2,01; 1,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,03</t>
+          <t>1,93; 6,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,34</t>
+          <t>-1,04; 2,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-20,88%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,11%</t>
+          <t>-8,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,14%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 135,93</t>
+          <t>-45,49; 105,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 249,43</t>
+          <t>7,36; 252,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,67; 73,16</t>
+          <t>-30,77; 183,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,31; 121,53</t>
+          <t>-75,74; 84,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,14; 638,9</t>
+          <t>16,87; 506,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 126,6</t>
+          <t>-63,73; 173,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 69,35</t>
+          <t>-42,88; 62,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,17; 252,52</t>
+          <t>40,66; 266,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 46,02</t>
+          <t>-25,17; 111,83</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1282,37 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,64</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2,92</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,61</t>
+          <t>-1,99; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,21</t>
+          <t>-0,02; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,35</t>
+          <t>-1,59; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,44</t>
+          <t>-2,05; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,41</t>
+          <t>2,38; 7,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 49,95</t>
+          <t>-2,22; 1,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,88</t>
+          <t>-1,51; 0,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,32</t>
+          <t>1,42; 4,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 38,25</t>
+          <t>-1,25; 1,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,41%</t>
+          <t>-2,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>446,13%</t>
+          <t>-2,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>271,45%</t>
+          <t>-0,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 26,56</t>
+          <t>-53,64; 33,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 134,76</t>
+          <t>-2,79; 120,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 52,86</t>
+          <t>-40,96; 48,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 73,02</t>
+          <t>-36,1; 75,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,5; 229,44</t>
+          <t>35,57; 205,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 1613,15</t>
+          <t>-37,8; 47,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 27,63</t>
+          <t>-36,41; 29,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,07; 147,44</t>
+          <t>34,62; 143,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 1165,88</t>
+          <t>-29,12; 41,47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,78</t>
+          <t>-2,32; 2,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,78</t>
+          <t>-0,48; 4,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,42</t>
+          <t>-1,61; 3,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,74</t>
+          <t>-1,52; 3,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,24</t>
+          <t>7,77; 14,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,26</t>
+          <t>-1,43; 2,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,67</t>
+          <t>-1,41; 2,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,12</t>
+          <t>4,45; 9,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,61</t>
+          <t>-1,06; 2,55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 145,37</t>
+          <t>-50,18; 135,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 272,18</t>
+          <t>-12,37; 258,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 250,93</t>
+          <t>-36,13; 193,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 96,72</t>
+          <t>-23,15; 97,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>112,35; 365,31</t>
+          <t>113,7; 363,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 60,5</t>
+          <t>-21,29; 77,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 73,75</t>
+          <t>-24,01; 71,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>82,41; 266,06</t>
+          <t>78,97; 267,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 74,4</t>
+          <t>-19,08; 75,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,59</t>
+          <t>-1,72; 2,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,87</t>
+          <t>-0,5; 4,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,56</t>
+          <t>-2,01; 2,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,33</t>
+          <t>-2,16; 1,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,39</t>
+          <t>4,57; 9,33</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,93</t>
+          <t>-2,1; 1,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,27</t>
+          <t>-1,74; 1,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,75</t>
+          <t>4,0; 8,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,56</t>
+          <t>-1,89; 1,25</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>-8,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>-3,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-2,92%</t>
+          <t>-6,18%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,98; 459,38</t>
+          <t>-79,08; 387,25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 679,35</t>
+          <t>-31,3; 588,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 552,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 30,08</t>
+          <t>-35,18; 36,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>73,03; 214,54</t>
+          <t>70,93; 205,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,99; 42,48</t>
+          <t>-35,18; 35,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 33,23</t>
+          <t>-32,66; 31,5</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>67,69; 197,61</t>
+          <t>73,27; 198,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 41,76</t>
+          <t>-33,98; 31,81</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,03</t>
+          <t>-0,58; 1,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,62</t>
+          <t>0,93; 2,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,27</t>
+          <t>-0,29; 1,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,34</t>
+          <t>-0,64; 1,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,7</t>
+          <t>5,22; 7,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 22,73</t>
+          <t>-0,79; 1,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,04</t>
+          <t>-0,39; 0,95</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,92</t>
+          <t>3,29; 4,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 12,79</t>
+          <t>-0,3; 0,94</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>117,28%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 42,63</t>
+          <t>-18,25; 45,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24,88; 113,15</t>
+          <t>29,88; 114,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 52,7</t>
+          <t>-9,07; 59,85</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 33,29</t>
+          <t>-12,66; 35,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>96,73; 186,76</t>
+          <t>101,92; 190,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 487,17</t>
+          <t>-15,57; 28,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 31,37</t>
+          <t>-9,34; 27,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>83,85; 149,16</t>
+          <t>81,4; 148,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 367,12</t>
+          <t>-7,31; 27,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
